--- a/data/Format=XLSX/Model=M10+/Floor=2/Location=Unit 210/Device=03/M10+_device03_11-10-2024 17:03:14.xlsx
+++ b/data/Format=XLSX/Model=M10+/Floor=2/Location=Unit 210/Device=03/M10+_device03_11-10-2024 17:03:14.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Downloads/M10+_device03_11-10-2024 17:03:"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3AA99B-69ED-8447-A666-E2A96DB2C41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA58104-3C3D-8E4A-A67A-187710CBE9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="880" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="593">
   <si>
     <t>NO.</t>
   </si>
@@ -1369,6 +1369,12 @@
     <t>2024-11-10 14:00:00(+08:00)</t>
   </si>
   <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>2024-11-10 15:00:00(+08:00)</t>
+  </si>
+  <si>
     <t>AQI</t>
   </si>
   <si>
@@ -1691,6 +1697,9 @@
   </si>
   <si>
     <t>775</t>
+  </si>
+  <si>
+    <t>781</t>
   </si>
   <si>
     <t>TVOC</t>
@@ -2141,7 +2150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -2165,19 +2174,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2194,13 +2203,13 @@
         <v>115</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>151</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>137</v>
@@ -2220,13 +2229,13 @@
         <v>98</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>134</v>
@@ -2246,13 +2255,13 @@
         <v>98</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>134</v>
@@ -2272,13 +2281,13 @@
         <v>96</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>132</v>
@@ -2298,13 +2307,13 @@
         <v>113</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>142</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>132</v>
@@ -2324,13 +2333,13 @@
         <v>145</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>142</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>134</v>
@@ -2350,13 +2359,13 @@
         <v>148</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>132</v>
@@ -2376,13 +2385,13 @@
         <v>148</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>129</v>
@@ -2402,13 +2411,13 @@
         <v>142</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>107</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>129</v>
@@ -2428,13 +2437,13 @@
         <v>126</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>129</v>
@@ -2454,13 +2463,13 @@
         <v>117</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>132</v>
@@ -2480,13 +2489,13 @@
         <v>110</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>129</v>
@@ -2506,13 +2515,13 @@
         <v>101</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>129</v>
@@ -2532,13 +2541,13 @@
         <v>92</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>126</v>
@@ -2558,13 +2567,13 @@
         <v>87</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>126</v>
@@ -2584,13 +2593,13 @@
         <v>87</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>123</v>
@@ -2610,13 +2619,13 @@
         <v>84</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>107</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>120</v>
@@ -2636,13 +2645,13 @@
         <v>78</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>117</v>
@@ -2662,13 +2671,13 @@
         <v>78</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>115</v>
@@ -2688,13 +2697,13 @@
         <v>78</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>145</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>115</v>
@@ -2714,13 +2723,13 @@
         <v>78</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>197</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>113</v>
@@ -2740,13 +2749,13 @@
         <v>72</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>218</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>110</v>
@@ -2766,13 +2775,13 @@
         <v>181</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>200</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>110</v>
@@ -2792,13 +2801,13 @@
         <v>156</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>179</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>120</v>
@@ -2818,13 +2827,13 @@
         <v>137</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>186</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>126</v>
@@ -2844,13 +2853,13 @@
         <v>123</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>184</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>142</v>
@@ -2870,13 +2879,13 @@
         <v>94</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>167</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>132</v>
@@ -2896,13 +2905,13 @@
         <v>66</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>134</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>117</v>
@@ -2922,13 +2931,13 @@
         <v>63</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>113</v>
@@ -2948,13 +2957,13 @@
         <v>87</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>117</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>113</v>
@@ -2974,13 +2983,13 @@
         <v>123</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>117</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>113</v>
@@ -3000,13 +3009,13 @@
         <v>145</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>110</v>
@@ -3026,13 +3035,13 @@
         <v>145</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>107</v>
@@ -3052,13 +3061,13 @@
         <v>110</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>96</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>107</v>
@@ -3078,13 +3087,13 @@
         <v>75</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>107</v>
@@ -3104,13 +3113,13 @@
         <v>53</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>104</v>
@@ -3130,13 +3139,13 @@
         <v>48</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>101</v>
@@ -3156,13 +3165,13 @@
         <v>45</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>96</v>
@@ -3182,13 +3191,13 @@
         <v>30</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>92</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>94</v>
@@ -3208,13 +3217,13 @@
         <v>30</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>94</v>
@@ -3234,13 +3243,13 @@
         <v>30</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>96</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>92</v>
@@ -3260,13 +3269,13 @@
         <v>33</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>92</v>
@@ -3286,13 +3295,13 @@
         <v>33</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>142</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>94</v>
@@ -3312,13 +3321,13 @@
         <v>151</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>224</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>98</v>
@@ -3338,13 +3347,13 @@
         <v>123</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>224</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>96</v>
@@ -3364,13 +3373,13 @@
         <v>129</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>194</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>94</v>
@@ -3390,13 +3399,13 @@
         <v>84</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>197</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>96</v>
@@ -3416,13 +3425,13 @@
         <v>58</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>176</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>96</v>
@@ -3442,13 +3451,13 @@
         <v>39</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>174</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>101</v>
@@ -3468,13 +3477,13 @@
         <v>30</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>179</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>104</v>
@@ -3494,13 +3503,13 @@
         <v>24</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>181</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>113</v>
@@ -3520,13 +3529,13 @@
         <v>30</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>181</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>115</v>
@@ -3546,13 +3555,13 @@
         <v>69</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>159</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>120</v>
@@ -3572,13 +3581,13 @@
         <v>117</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>148</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>132</v>
@@ -3598,13 +3607,13 @@
         <v>137</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>167</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>140</v>
@@ -3624,13 +3633,13 @@
         <v>134</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>137</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>137</v>
@@ -3650,13 +3659,13 @@
         <v>134</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>107</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>129</v>
@@ -3676,13 +3685,13 @@
         <v>117</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>90</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>117</v>
@@ -3702,13 +3711,13 @@
         <v>72</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>113</v>
@@ -3728,13 +3737,13 @@
         <v>69</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>92</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>107</v>
@@ -3754,13 +3763,13 @@
         <v>60</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>81</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>98</v>
@@ -3780,13 +3789,13 @@
         <v>53</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>81</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>94</v>
@@ -3806,13 +3815,13 @@
         <v>45</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>90</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>92</v>
@@ -3832,13 +3841,13 @@
         <v>42</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>92</v>
@@ -3858,13 +3867,13 @@
         <v>42</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>92</v>
@@ -3884,13 +3893,13 @@
         <v>45</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>92</v>
@@ -3910,13 +3919,13 @@
         <v>48</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>154</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>92</v>
@@ -3936,13 +3945,13 @@
         <v>56</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>184</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>92</v>
@@ -3962,13 +3971,13 @@
         <v>72</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>215</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>90</v>
@@ -3988,13 +3997,13 @@
         <v>162</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>337</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>90</v>
@@ -4014,13 +4023,13 @@
         <v>162</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>186</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>90</v>
@@ -4040,13 +4049,13 @@
         <v>151</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>154</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>87</v>
@@ -4066,13 +4075,13 @@
         <v>142</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>148</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>90</v>
@@ -4092,13 +4101,13 @@
         <v>156</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>162</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>90</v>
@@ -4118,13 +4127,13 @@
         <v>246</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>179</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>87</v>
@@ -4144,13 +4153,13 @@
         <v>221</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>142</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>78</v>
@@ -4170,13 +4179,13 @@
         <v>212</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>78</v>
@@ -4196,13 +4205,13 @@
         <v>206</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>107</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>69</v>
@@ -4222,13 +4231,13 @@
         <v>194</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>92</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>63</v>
@@ -4248,13 +4257,13 @@
         <v>181</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>90</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>58</v>
@@ -4274,13 +4283,13 @@
         <v>132</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>87</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>58</v>
@@ -4300,13 +4309,13 @@
         <v>58</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>90</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>56</v>
@@ -4326,13 +4335,13 @@
         <v>48</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>56</v>
@@ -4352,13 +4361,13 @@
         <v>45</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>56</v>
@@ -4378,13 +4387,13 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>56</v>
@@ -4404,13 +4413,13 @@
         <v>27</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>56</v>
@@ -4430,13 +4439,13 @@
         <v>27</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>96</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>58</v>
@@ -4456,13 +4465,13 @@
         <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>58</v>
@@ -4482,13 +4491,13 @@
         <v>27</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>104</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>58</v>
@@ -4508,13 +4517,13 @@
         <v>27</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>63</v>
@@ -4534,13 +4543,13 @@
         <v>36</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>159</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>72</v>
@@ -4560,13 +4569,13 @@
         <v>42</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>179</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>66</v>
@@ -4586,13 +4595,13 @@
         <v>66</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>215</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>63</v>
@@ -4612,13 +4621,13 @@
         <v>69</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>212</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>60</v>
@@ -4638,13 +4647,13 @@
         <v>75</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>203</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>63</v>
@@ -4664,13 +4673,13 @@
         <v>75</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>167</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>66</v>
@@ -4690,13 +4699,13 @@
         <v>75</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>172</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>69</v>
@@ -4716,13 +4725,13 @@
         <v>60</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>167</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>69</v>
@@ -4742,13 +4751,13 @@
         <v>56</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>164</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>78</v>
@@ -4768,13 +4777,13 @@
         <v>156</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>96</v>
@@ -4794,13 +4803,13 @@
         <v>151</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>164</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>90</v>
@@ -4820,13 +4829,13 @@
         <v>145</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>154</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>92</v>
@@ -4846,13 +4855,13 @@
         <v>142</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>134</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>96</v>
@@ -4872,13 +4881,13 @@
         <v>154</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>96</v>
@@ -4898,13 +4907,13 @@
         <v>142</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>96</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>90</v>
@@ -4924,13 +4933,13 @@
         <v>134</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>92</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>87</v>
@@ -4950,13 +4959,13 @@
         <v>87</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>96</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>84</v>
@@ -4976,13 +4985,13 @@
         <v>63</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>87</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>78</v>
@@ -5002,13 +5011,13 @@
         <v>53</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>84</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>66</v>
@@ -5028,13 +5037,13 @@
         <v>33</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>84</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>60</v>
@@ -5054,13 +5063,13 @@
         <v>27</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>90</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>58</v>
@@ -5080,13 +5089,13 @@
         <v>24</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>56</v>
@@ -5106,13 +5115,13 @@
         <v>21</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>56</v>
@@ -5132,13 +5141,13 @@
         <v>18</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>56</v>
@@ -5158,13 +5167,13 @@
         <v>21</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>142</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>56</v>
@@ -5184,13 +5193,13 @@
         <v>186</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>209</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>63</v>
@@ -5210,13 +5219,13 @@
         <v>115</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>396</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>63</v>
@@ -5236,13 +5245,13 @@
         <v>117</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>58</v>
@@ -5262,13 +5271,13 @@
         <v>113</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>189</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>56</v>
@@ -5288,13 +5297,13 @@
         <v>212</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>162</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>58</v>
@@ -5314,13 +5323,13 @@
         <v>167</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>244</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>63</v>
@@ -5340,13 +5349,13 @@
         <v>137</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>159</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>69</v>
@@ -5366,13 +5375,13 @@
         <v>113</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>151</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>66</v>
@@ -5392,13 +5401,13 @@
         <v>129</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>154</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>69</v>
@@ -5418,13 +5427,13 @@
         <v>134</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>132</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>72</v>
@@ -5444,13 +5453,13 @@
         <v>142</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>75</v>
@@ -5470,13 +5479,13 @@
         <v>151</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>148</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>81</v>
@@ -5496,13 +5505,13 @@
         <v>156</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>84</v>
@@ -5522,13 +5531,13 @@
         <v>148</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>92</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>78</v>
@@ -5548,13 +5557,13 @@
         <v>120</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>84</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>69</v>
@@ -5574,13 +5583,13 @@
         <v>104</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>92</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>63</v>
@@ -5600,13 +5609,13 @@
         <v>92</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>60</v>
@@ -5626,13 +5635,13 @@
         <v>75</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>92</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>60</v>
@@ -5652,13 +5661,13 @@
         <v>58</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>104</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>60</v>
@@ -5678,13 +5687,13 @@
         <v>53</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>63</v>
@@ -5704,13 +5713,13 @@
         <v>53</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>66</v>
@@ -5730,13 +5739,13 @@
         <v>56</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H138" s="1" t="s">
         <v>69</v>
@@ -5756,13 +5765,13 @@
         <v>56</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>117</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>66</v>
@@ -5782,13 +5791,13 @@
         <v>60</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>169</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>72</v>
@@ -5808,13 +5817,13 @@
         <v>60</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>191</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>75</v>
@@ -5834,13 +5843,13 @@
         <v>66</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>197</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>69</v>
@@ -5860,13 +5869,13 @@
         <v>81</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>186</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>63</v>
@@ -5886,13 +5895,13 @@
         <v>169</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>186</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="H144" s="1" t="s">
         <v>63</v>
@@ -5912,13 +5921,13 @@
         <v>169</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>181</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>66</v>
@@ -5938,13 +5947,13 @@
         <v>176</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>169</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>69</v>
@@ -5964,13 +5973,13 @@
         <v>172</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>197</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H147" s="1" t="s">
         <v>75</v>
@@ -5990,13 +5999,13 @@
         <v>164</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>215</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>78</v>
@@ -6016,13 +6025,13 @@
         <v>159</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>174</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>72</v>
@@ -6042,13 +6051,13 @@
         <v>154</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>72</v>
@@ -6068,13 +6077,13 @@
         <v>154</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>151</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>92</v>
@@ -6094,13 +6103,13 @@
         <v>169</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>174</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>98</v>
@@ -6120,13 +6129,13 @@
         <v>319</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>104</v>
@@ -6146,13 +6155,13 @@
         <v>203</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>104</v>
@@ -6172,13 +6181,13 @@
         <v>179</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H155" s="1" t="s">
         <v>107</v>
@@ -6198,13 +6207,13 @@
         <v>172</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>110</v>
@@ -6224,13 +6233,13 @@
         <v>167</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="H157" s="1" t="s">
         <v>101</v>
@@ -6250,13 +6259,13 @@
         <v>164</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>84</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>92</v>
@@ -6276,13 +6285,13 @@
         <v>159</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>87</v>
@@ -6302,13 +6311,13 @@
         <v>154</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>87</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H160" s="1" t="s">
         <v>87</v>
@@ -6328,13 +6337,13 @@
         <v>151</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>92</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="H161" s="1" t="s">
         <v>84</v>
@@ -6354,13 +6363,13 @@
         <v>151</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="H162" s="1" t="s">
         <v>84</v>
@@ -6380,13 +6389,13 @@
         <v>148</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>104</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>84</v>
@@ -6406,13 +6415,13 @@
         <v>200</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>145</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>81</v>
@@ -6432,13 +6441,13 @@
         <v>191</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>218</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>81</v>
@@ -6458,13 +6467,13 @@
         <v>191</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>236</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>81</v>
@@ -6484,13 +6493,13 @@
         <v>176</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>218</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>78</v>
@@ -6510,13 +6519,13 @@
         <v>164</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>194</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H168" s="1" t="s">
         <v>87</v>
@@ -6536,16 +6545,42 @@
         <v>164</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>200</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="H169" s="1" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A170" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
